--- a/MiniTemplate/Datas/grow2.xlsx
+++ b/MiniTemplate/Datas/grow2.xlsx
@@ -1,25 +1,41 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9AFB16-8B1A-48B7-809F-C9E3B08AEC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>工作表</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>Sheet1</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>openpyxl</dc:creator>
+  <cp:lastModifiedBy>凌龙 邹</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-10-24T07:10:53Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-10-26T11:36:23Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
   <si>
     <t>##var</t>
@@ -97,24 +113,12 @@
     <t>经营</t>
   </si>
   <si>
-    <t>WorkIncomePct</t>
-  </si>
-  <si>
     <t>探索</t>
   </si>
   <si>
-    <t>ShopDiscountPct</t>
-  </si>
-  <si>
     <t>FishRarePct</t>
   </si>
   <si>
-    <t>OfflineCapHours</t>
-  </si>
-  <si>
-    <t>MissionRewardPct</t>
-  </si>
-  <si>
     <t>LotteryLuck</t>
   </si>
   <si>
@@ -211,12 +215,28 @@
   </si>
   <si>
     <t>钓鱼获得稀有鱼概率小幅提升</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WorkIncome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Health</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissionReward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShopDiscount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -273,7 +293,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -556,18 +576,38 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3557982-E4D4-4AD5-B067-BF19AB0E53F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="19.625" customWidth="1"/>
-    <col min="7" max="7" width="21.25" customWidth="1"/>
-    <col min="8" max="8" width="13.875" customWidth="1"/>
-    <col min="9" max="9" width="30.25" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="7" max="7" width="21.21875" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="30.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +636,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -625,7 +665,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -654,7 +694,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -674,16 +714,16 @@
         <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
         <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -706,18 +746,18 @@
         <v>2</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E6">
         <v>1001</v>
@@ -726,21 +766,21 @@
         <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -752,24 +792,24 @@
         <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>1001</v>
@@ -778,24 +818,24 @@
         <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>1002</v>
@@ -804,21 +844,21 @@
         <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -830,24 +870,24 @@
         <v>75</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <v>1004</v>
@@ -856,24 +896,24 @@
         <v>75</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>1005</v>
@@ -882,21 +922,21 @@
         <v>120</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -908,24 +948,24 @@
         <v>120</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14">
         <v>1007</v>
@@ -934,13 +974,13 @@
         <v>120</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H14">
         <v>5</v>
       </c>
       <c r="I14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
